--- a/gunluk_ornek.xlsx
+++ b/gunluk_ornek.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rose0\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{306184E5-EB26-43B8-B214-7576A56B3A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{968DD5DA-E5D1-4A08-A180-72CDC4DB9BC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8C3FF7E0-4C03-4688-9A83-393CF89114FC}"/>
   </bookViews>
@@ -905,7 +905,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C659B5D1-DCA3-498F-BABC-47E82E26E12C}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.21875" customWidth="1"/>
@@ -1023,21 +1023,33 @@
         <v>467</v>
       </c>
     </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B15">
+        <v>11667</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B16">
+        <v>66090</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>46310</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Belge" ma:contentTypeID="0x0101001A6E40365F939B48B3B82312979B8069" ma:contentTypeVersion="16" ma:contentTypeDescription="Yeni belge oluşturun." ma:contentTypeScope="" ma:versionID="8517e8cfcf5ab74914cba8889ffe32a7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="5f896036-3b44-4bf0-b937-b8ae48953dec" xmlns:ns4="70f9ab84-23fb-41b5-a191-ad5bb675a186" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1d017b8a2c99e1490a5f31ec58fdf559" ns3:_="" ns4:_="">
     <xsd:import namespace="5f896036-3b44-4bf0-b937-b8ae48953dec"/>
@@ -1278,6 +1290,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1287,14 +1308,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5A63104-9D16-4103-9C7F-2F0CDACFF919}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B98ADEA-BAA5-4724-867F-69A05CFCD43E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1309,6 +1322,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5A63104-9D16-4103-9C7F-2F0CDACFF919}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/gunluk_ornek.xlsx
+++ b/gunluk_ornek.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rose0\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{968DD5DA-E5D1-4A08-A180-72CDC4DB9BC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{316BC343-394C-432A-8664-5CC4B1D93F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8C3FF7E0-4C03-4688-9A83-393CF89114FC}"/>
   </bookViews>
@@ -1039,9 +1039,12 @@
         <v>66090</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46310</v>
+      </c>
+      <c r="B17">
+        <v>73718</v>
       </c>
     </row>
   </sheetData>
@@ -1050,6 +1053,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Belge" ma:contentTypeID="0x0101001A6E40365F939B48B3B82312979B8069" ma:contentTypeVersion="16" ma:contentTypeDescription="Yeni belge oluşturun." ma:contentTypeScope="" ma:versionID="8517e8cfcf5ab74914cba8889ffe32a7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="5f896036-3b44-4bf0-b937-b8ae48953dec" xmlns:ns4="70f9ab84-23fb-41b5-a191-ad5bb675a186" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1d017b8a2c99e1490a5f31ec58fdf559" ns3:_="" ns4:_="">
     <xsd:import namespace="5f896036-3b44-4bf0-b937-b8ae48953dec"/>
@@ -1290,15 +1302,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1308,6 +1311,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5A63104-9D16-4103-9C7F-2F0CDACFF919}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B98ADEA-BAA5-4724-867F-69A05CFCD43E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1322,14 +1333,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5A63104-9D16-4103-9C7F-2F0CDACFF919}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/gunluk_ornek.xlsx
+++ b/gunluk_ornek.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rose0\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{316BC343-394C-432A-8664-5CC4B1D93F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{152255B1-816A-4DFC-B85E-887F7AFC08D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8C3FF7E0-4C03-4688-9A83-393CF89114FC}"/>
   </bookViews>
   <sheets>
     <sheet name="gunluk_ornek - Kopya" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -905,7 +918,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C659B5D1-DCA3-498F-BABC-47E82E26E12C}">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.21875" customWidth="1"/>
@@ -1047,21 +1060,65 @@
         <v>73718</v>
       </c>
     </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B18">
+        <v>73851</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>46312</v>
+      </c>
+      <c r="B19">
+        <v>38103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>46313</v>
+      </c>
+      <c r="B20">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>46314</v>
+      </c>
+      <c r="B21">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B22">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B23">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>46317</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Belge" ma:contentTypeID="0x0101001A6E40365F939B48B3B82312979B8069" ma:contentTypeVersion="16" ma:contentTypeDescription="Yeni belge oluşturun." ma:contentTypeScope="" ma:versionID="8517e8cfcf5ab74914cba8889ffe32a7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="5f896036-3b44-4bf0-b937-b8ae48953dec" xmlns:ns4="70f9ab84-23fb-41b5-a191-ad5bb675a186" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1d017b8a2c99e1490a5f31ec58fdf559" ns3:_="" ns4:_="">
     <xsd:import namespace="5f896036-3b44-4bf0-b937-b8ae48953dec"/>
@@ -1302,6 +1359,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1311,14 +1377,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5A63104-9D16-4103-9C7F-2F0CDACFF919}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B98ADEA-BAA5-4724-867F-69A05CFCD43E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1333,6 +1391,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5A63104-9D16-4103-9C7F-2F0CDACFF919}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
